--- a/산출물/단위테스트명세서.xlsx
+++ b/산출물/단위테스트명세서.xlsx
@@ -93,14 +93,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="48" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="7" max="7" width="7" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
@@ -152,7 +152,7 @@
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인증 토큰</t>
+          <t xml:space="preserve">회원가입·로그인·프로젝트 진입</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -162,17 +162,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">refresh 토큰이 매번 무작위이며 DB에는 원문이 아닌 해시만 저장되는지 확인한다.</t>
+          <t xml:space="preserve">회원가입 후 정상·오류 로그인을 수행한다.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 사용자 토큰 2개</t>
+          <t xml:space="preserve">정상 계정·중복 ID·틀린 비밀번호</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두 토큰 원문이 다르고 저장 가능한 값은 해시다.</t>
+          <t xml:space="preserve">정상 가입·로그인만 성공하고 오류 계약이 구분된다.</t>
         </is>
       </c>
       <c r="G2" s="3"/>
@@ -188,17 +188,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효 입력은 생성하고 중복 로그인 ID·이메일 및 잘못된 입력은 차단하는 API 동작을 확인한다.</t>
+          <t xml:space="preserve">access 만료 후 refresh로 갱신하고 이전 refresh를 재사용한다.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상·중복 ID·중복 이메일·빈 값</t>
+          <t xml:space="preserve">유효·사용 완료 refresh</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 입력만 계정이 생성되고 오류별 계약 코드가 반환된다.</t>
+          <t xml:space="preserve">토큰이 회전하며 이전 refresh는 401이다.</t>
         </is>
       </c>
       <c r="G3" s="3"/>
@@ -214,17 +214,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 비밀번호와 틀린 비밀번호의 발급·401 경계를 확인한다.</t>
+          <t xml:space="preserve">로그아웃 뒤 같은 refresh로 다시 갱신한다.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">등록 계정·틀린 비밀번호</t>
+          <t xml:space="preserve">로그아웃 세션</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 계정만 access·refresh 토큰을 받는다.</t>
+          <t xml:space="preserve">재사용이 차단된다.</t>
         </is>
       </c>
       <c r="G4" s="3"/>
@@ -240,17 +240,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">refresh 사용 시 새 토큰을 발급하고 이전 토큰 재사용을 차단하는 동작을 확인한다.</t>
+          <t xml:space="preserve">프로젝트를 생성하고 생성자 역할을 확인한다.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효 refresh·이미 사용한 refresh</t>
+          <t xml:space="preserve">신규 프로젝트</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">최초 갱신만 성공하고 재사용은 401이다.</t>
+          <t xml:space="preserve">생성자가 OWNER다.</t>
         </is>
       </c>
       <c r="G5" s="3"/>
@@ -266,17 +266,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">로그아웃 시 revoked_at을 기록하고 같은 refresh의 재사용을 차단한다.</t>
+          <t xml:space="preserve">세 역할로 허용·금지 동작과 다른 프로젝트 직접 URL을 확인한다.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">로그인 세션 1건</t>
+          <t xml:space="preserve">OWNER·EDITOR·VIEWER·비멤버</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">로그아웃 뒤 갱신이 401로 차단된다.</t>
+          <t xml:space="preserve">역할표와 일치하고 비멤버는 404다.</t>
         </is>
       </c>
       <c r="G6" s="3"/>
@@ -284,25 +284,29 @@
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 초대·멤버 관리</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">만료·위조·누락 access token이 모두 보호 API에서 차단되는지 확인한다.</t>
+          <t xml:space="preserve">OWNER가 EDITOR 초대를 발송하고 중복 초대를 시도한다.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상·만료·위조·누락 토큰</t>
+          <t xml:space="preserve">동일 사용자 2회</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 토큰만 통과하고 나머지는 401이다.</t>
+          <t xml:space="preserve">첫 초대만 생성되고 중복은 409다.</t>
         </is>
       </c>
       <c r="G7" s="3"/>
@@ -310,29 +314,25 @@
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="3"/>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트·초대·역할</t>
-        </is>
-      </c>
+      <c r="B8" s="4"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER가 프로젝트 수정을 할 수 없는지 확인한다.</t>
+          <t xml:space="preserve">초대받은 사용자가 목록을 보고 수락한다.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER 멤버</t>
+          <t xml:space="preserve">PENDING 초대</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROJECT_FORBIDDEN 403이다.</t>
+          <t xml:space="preserve">멤버가 되고 프로젝트 목록에 나타난다.</t>
         </is>
       </c>
       <c r="G8" s="3"/>
@@ -343,22 +343,22 @@
       <c r="B9" s="4"/>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">실제 OWNER만 멤버 관리와 프로젝트 삭제를 수행하는지 확인한다.</t>
+          <t xml:space="preserve">다른 초대를 거절하고 OWNER가 보낸 초대를 취소한다.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER·EDITOR 계정</t>
+          <t xml:space="preserve">PENDING 초대 2건</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER만 관리·삭제할 수 있다.</t>
+          <t xml:space="preserve">REJECTED·CANCELLED가 보존되고 수락할 수 없다.</t>
         </is>
       </c>
       <c r="G9" s="3"/>
@@ -369,22 +369,22 @@
       <c r="B10" s="4"/>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 사용자에게 PENDING 초대를 두 번 보낼 수 없는지 확인한다.</t>
+          <t xml:space="preserve">OWNER가 멤버 역할을 VIEWER로 바꾼다.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 프로젝트·동일 피초대자</t>
+          <t xml:space="preserve">EDITOR 멤버</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두 번째 초대가 충돌로 차단된다.</t>
+          <t xml:space="preserve">즉시 편집 API가 403이다.</t>
         </is>
       </c>
       <c r="G10" s="3"/>
@@ -395,22 +395,22 @@
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 생성과 생성자 OWNER 등록의 원자성을 확인한다.</t>
+          <t xml:space="preserve">멤버를 제외하고 기존 세션으로 재접근한다.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 사용자·프로젝트명</t>
+          <t xml:space="preserve">로그인 유지 세션</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트와 OWNER 멤버가 함께 생성된다.</t>
+          <t xml:space="preserve">모든 프로젝트 경로가 404다.</t>
         </is>
       </c>
       <c r="G11" s="3"/>
@@ -418,25 +418,29 @@
     </row>
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="3"/>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다중 문서 업로드·목록 조회</t>
+        </is>
+      </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">내가 멤버인 프로젝트만 반환하는 API 동작을 확인한다.</t>
+          <t xml:space="preserve">지원 파일 5종을 다중 업로드한다.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">멤버 프로젝트 2건·비멤버 1건</t>
+          <t xml:space="preserve">PDF·DOCX·HWPX·JPG·PNG</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">멤버 프로젝트 2건만 반환된다.</t>
+          <t xml:space="preserve">각 문서 ID가 즉시 반환되고 PENDING이다.</t>
         </is>
       </c>
       <c r="G12" s="3"/>
@@ -447,22 +451,22 @@
       <c r="B13" s="4"/>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING에서 ACCEPTED·REJECTED·CANCELLED로 가는 상태 전이를 각각 확인한다.</t>
+          <t xml:space="preserve">형식·크기·빈 파일·중복·경로 조작 오류를 유도한다.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">초대 3건</t>
+          <t xml:space="preserve">오류 파일 세트</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 최종 상태와 멤버 생성 여부가 계약과 일치한다.</t>
+          <t xml:space="preserve">유효 파일만 저장되고 원인별 오류다.</t>
         </is>
       </c>
       <c r="G13" s="3"/>
@@ -473,22 +477,22 @@
       <c r="B14" s="4"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">역할 변경 직후 허용 동작이 바뀌는지 확인한다.</t>
+          <t xml:space="preserve">문서 처리 상태가 완료될 때까지 확인한다.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDITOR→VIEWER</t>
+          <t xml:space="preserve">텍스트·스캔 문서</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경 직후 편집 API가 403이다.</t>
+          <t xml:space="preserve">추출 방식과 EXTRACTED 상태가 기록된다.</t>
         </is>
       </c>
       <c r="G14" s="3"/>
@@ -499,22 +503,22 @@
       <c r="B15" s="4"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제외된 멤버가 즉시 프로젝트 데이터에 접근할 수 없는지 확인한다.</t>
+          <t xml:space="preserve">한 건을 실패시킨 뒤 재처리한다.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 멤버 1명</t>
+          <t xml:space="preserve">추출기 실패 문서</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제외 후 모든 프로젝트 API가 404다.</t>
+          <t xml:space="preserve">오류가 보이고 재처리 후 완료 또는 명시적 실패다.</t>
         </is>
       </c>
       <c r="G15" s="3"/>
@@ -525,22 +529,22 @@
       <c r="B16" s="4"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서·태스크가 있는 프로젝트 삭제 시 하위 데이터 정리를 확인한다.</t>
+          <t xml:space="preserve">문서를 21건으로 만들고 2페이지로 이동한다.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하위 문서·태스크 포함 프로젝트</t>
+          <t xml:space="preserve">21건·size 20</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트와 하위 데이터가 함께 정리된다.</t>
+          <t xml:space="preserve">1페이지 20건, 2페이지 1건이며 URL page가 유지된다.</t>
         </is>
       </c>
       <c r="G16" s="3"/>
@@ -548,29 +552,25 @@
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="A17" s="3"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드·추출</t>
-        </is>
-      </c>
+      <c r="B17" s="4"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">업로드 요청이 추출기를 직접 실행하지 않고 PENDING 문서를 만드는지 확인한다.</t>
+          <t xml:space="preserve">필터를 변경하고 새로고침한다.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 파일</t>
+          <t xml:space="preserve">2페이지에서 유형 필터</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 문서가 생성되고 extractor는 호출되지 않는다.</t>
+          <t xml:space="preserve">page가 초기화되고 필터 상태가 일관된다.</t>
         </is>
       </c>
       <c r="G17" s="3"/>
@@ -578,25 +578,29 @@
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 검수·최신 검색 반영</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker가 문서를 EXTRACTED로 전이하는지 확인한다.</t>
+          <t xml:space="preserve">검수 화면에서 이미지·박스·신뢰도를 확인하고 확대한다.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 문서</t>
+          <t xml:space="preserve">스캔 문서</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출텍스트 저장 후 EXTRACTED가 된다.</t>
+          <t xml:space="preserve">모든 배율에서 박스와 문자가 일치한다.</t>
         </is>
       </c>
       <c r="G18" s="3"/>
@@ -607,22 +611,22 @@
       <c r="B19" s="4"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출 실패 원인과 FAILED 상태를 저장하는지 확인한다.</t>
+          <t xml:space="preserve">텍스트·좌표·단락·읽기 순서를 수정한다.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출기 예외</t>
+          <t xml:space="preserve">오탈자·2단·표 문서</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAILED와 processing_error가 저장된다.</t>
+          <t xml:space="preserve">원문 보존, version 증가, 본문 순서가 정확하다.</t>
         </is>
       </c>
       <c r="G19" s="3"/>
@@ -633,22 +637,22 @@
       <c r="B20" s="4"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAILED 문서를 재시도 가능한 상태로 돌리는지 확인한다.</t>
+          <t xml:space="preserve">박스를 생성·제외·복원하고 병합·분리한다.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAILED 문서</t>
+          <t xml:space="preserve">OCR 요소 다건</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오류가 초기화되고 다시 큐에 넣을 수 있다.</t>
+          <t xml:space="preserve">현재 포함 요소만 확정 본문에 반영된다.</t>
         </is>
       </c>
       <c r="G20" s="3"/>
@@ -659,22 +663,22 @@
       <c r="B21" s="4"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 프로젝트의 같은 파일은 허용하고 같은 프로젝트 중복만 차단하는지 확인한다.</t>
+          <t xml:space="preserve">두 세션에서 같은 요소를 수정한다.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 해시·서로 다른 프로젝트</t>
+          <t xml:space="preserve">동일 version 동시 요청</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중복 판정이 요청 프로젝트 안에서만 적용된다.</t>
+          <t xml:space="preserve">나중 요청은 409이며 부분 변경이 없다.</t>
         </is>
       </c>
       <c r="G21" s="3"/>
@@ -685,22 +689,22 @@
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCX 원문이 제한을 넘으면 이미지 OCR 전에 차단되는지 확인한다.</t>
+          <t xml:space="preserve">검수를 완료하고 재청킹 상태를 확인한다.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제한 초과 DOCX</t>
+          <t xml:space="preserve">수정 완료 문서</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENT_TEXT_TOO_LARGE가 발생한다.</t>
+          <t xml:space="preserve">확정 리비전과 재인덱싱 작업이 연결된다.</t>
         </is>
       </c>
       <c r="G22" s="3"/>
@@ -711,22 +715,22 @@
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">희소 텍스트와 큰 스캔 이미지 조합에서 전체 페이지 OCR을 선택하는지 확인한다.</t>
+          <t xml:space="preserve">검색에서 수정 전·후 문구를 조회한다.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">희소 텍스트 레이어 PDF</t>
+          <t xml:space="preserve">이전 문구·새 문구</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">full-page OCR 전략을 선택한다.</t>
+          <t xml:space="preserve">새 근거만 최신 결과로 표시된다.</t>
         </is>
       </c>
       <c r="G23" s="3"/>
@@ -734,25 +738,29 @@
     </row>
     <row r="24" ht="38" customHeight="1">
       <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항·일정 분석·검토</t>
+        </is>
+      </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7종 유형만 허용하고 입력을 정규화하는지 확인한다.</t>
+          <t xml:space="preserve">회의록 분석을 실행하고 job 상태를 조회한다.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상·미지원 유형</t>
+          <t xml:space="preserve">결정·일정 포함 회의록</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 유형만 표준 enum 값으로 저장된다.</t>
+          <t xml:space="preserve">두 분석기가 완료되고 PENDING 후보가 생긴다.</t>
         </is>
       </c>
       <c r="G24" s="3"/>
@@ -763,22 +771,22 @@
       <c r="B25" s="4"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지원 형식·20MB·빈 파일·확장자 위장·경로 조작 파일명을 API 수준에서 확인한다.</t>
+          <t xml:space="preserve">결정 후보를 승인·수정 승인·거절·취소한다.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDF·DOCX·HWPX·JPG·PNG 및 오류 파일</t>
+          <t xml:space="preserve">결정 후보 4건</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효 파일만 저장되고 오류별 코드가 구분된다.</t>
+          <t xml:space="preserve">상태·결정자·시각이 기록된다.</t>
         </is>
       </c>
       <c r="G25" s="3"/>
@@ -789,22 +797,22 @@
       <c r="B26" s="4"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 21건에서 2페이지 이동과 필터 변경 시 page 초기화를 확인한다.</t>
+          <t xml:space="preserve">일정 후보도 같은 네 상태로 처리한다.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 21건·size 20</t>
+          <t xml:space="preserve">일정 후보 4건</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1페이지 20건, 2페이지 1건이며 URL page가 유지된다.</t>
+          <t xml:space="preserve">승인 항목만 하류 데이터가 된다.</t>
         </is>
       </c>
       <c r="G26" s="3"/>
@@ -812,29 +820,25 @@
     </row>
     <row r="27" ht="38" customHeight="1">
       <c r="A27" s="3"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 검수</t>
-        </is>
-      </c>
+      <c r="B27" s="4"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">부분 필드 수정 요청을 허용하는지 확인한다.</t>
+          <t xml:space="preserve">결정사항 대장과 다음 회의 안건을 미리 본다.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">text만 포함한 변경</t>
+          <t xml:space="preserve">승인 결정·PENDING 도메인 결정</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효한 부분 수정으로 파싱된다.</t>
+          <t xml:space="preserve">대장은 승인 결정 전체, 안건은 PENDING 결정만 포함한다.</t>
         </is>
       </c>
       <c r="G27" s="3"/>
@@ -845,22 +849,22 @@
       <c r="B28" s="4"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">잘못된 좌표를 스키마에서 차단하는지 확인한다.</t>
+          <t xml:space="preserve">분석 완료 뒤 대시보드·산출물 화면을 다시 연다.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">음수·역전 좌표</t>
+          <t xml:space="preserve">COMPLETED job</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422 validation 오류다.</t>
+          <t xml:space="preserve">새 승인 대기·산출물 재료가 새로고침된다.</t>
         </is>
       </c>
       <c r="G28" s="3"/>
@@ -868,25 +872,29 @@
     </row>
     <row r="29" ht="38" customHeight="1">
       <c r="A29" s="3"/>
-      <c r="B29" s="4"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">액션 아이템 승인·태스크 완료</t>
+        </is>
+      </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 박스가 좌표 순서에 맞게 본문과 reading_order에 삽입되는지 확인한다.</t>
+          <t xml:space="preserve">계약 문서를 분석해 PENDING 액션 제안을 만든다.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존 2박스 사이 좌표</t>
+          <t xml:space="preserve">명시적 수행 의무가 있는 계약서</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">본문·reading_order 모두 중간에 삽입된다.</t>
+          <t xml:space="preserve">원문 근거가 있는 후보만 생성된다.</t>
         </is>
       </c>
       <c r="G29" s="3"/>
@@ -897,22 +905,22 @@
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2단 페이지가 열 우선으로 읽히는지 확인한다.</t>
+          <t xml:space="preserve">제안 하나를 승인한다.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌·우 2단 요소</t>
+          <t xml:space="preserve">PENDING 제안</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">왼쪽 열 전체 뒤 오른쪽 열 순서다.</t>
+          <t xml:space="preserve">AI_APPROVED 태스크 한 건이 생긴다.</t>
         </is>
       </c>
       <c r="G30" s="3"/>
@@ -923,22 +931,22 @@
       <c r="B31" s="4"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">표 행 구조 메타데이터가 청킹까지 보존되는지 확인한다.</t>
+          <t xml:space="preserve">다른 제안을 거절한다.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">표 OCR 요소</t>
+          <t xml:space="preserve">PENDING 제안</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">행·열 구조 메타데이터가 응답에 남는다.</t>
+          <t xml:space="preserve">보드에는 안 보이고 거절 이력에 남는다.</t>
         </is>
       </c>
       <c r="G31" s="3"/>
@@ -949,22 +957,22 @@
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">잠근 행을 읽은 뒤 version을 비교하는지 확인한다.</t>
+          <t xml:space="preserve">태스크를 수정하고 칸반에서 DONE으로 옮긴다.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 요소의 오래된 version</t>
+          <t xml:space="preserve">승인된 태스크</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오래된 요청은 충돌로 거부된다.</t>
+          <t xml:space="preserve">상태와 completed_at이 기록된다.</t>
         </is>
       </c>
       <c r="G32" s="3"/>
@@ -975,22 +983,22 @@
       <c r="B33" s="4"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 항목이 stale이면 전체 수정이 롤백되는지 확인한다.</t>
+          <t xml:space="preserve">같은 문서를 재분석한다.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 1건·stale 1건</t>
+          <t xml:space="preserve">동일 근거</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두 항목 모두 변경되지 않는다.</t>
+          <t xml:space="preserve">검토 완료 후보·태스크는 중복 생성되지 않는다.</t>
         </is>
       </c>
       <c r="G33" s="3"/>
@@ -998,25 +1006,29 @@
     </row>
     <row r="34" ht="38" customHeight="1">
       <c r="A34" s="3"/>
-      <c r="B34" s="4"/>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 추출·검토·현황 갱신</t>
+        </is>
+      </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">단락 변경이 text_version을 한 번 올리고 청크를 stale로 표시하는지 확인한다.</t>
+          <t xml:space="preserve">금액 분석을 실행하고 PENDING 결과를 확인한다.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">paragraph 변경</t>
+          <t xml:space="preserve">수량·단가·총액·부가세 문서</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버전은 1회 증가하고 stale 표시가 남는다.</t>
+          <t xml:space="preserve">원문 근거와 revision을 가진 PENDING 항목이 생긴다.</t>
         </is>
       </c>
       <c r="G34" s="3"/>
@@ -1027,22 +1039,22 @@
       <c r="B35" s="4"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR과 검수 이미지가 같은 EXIF 정규화 결과를 쓰는지 확인한다.</t>
+          <t xml:space="preserve">승인·수정 승인·거절·취소를 각각 수행한다.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">회전 EXIF 이미지</t>
+          <t xml:space="preserve">후보 4건</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 좌표와 검수 이미지 방향이 일치한다.</t>
+          <t xml:space="preserve">검토 상태와 수정 가능 필드 계약이 지켜진다.</t>
         </is>
       </c>
       <c r="G35" s="3"/>
@@ -1053,22 +1065,22 @@
       <c r="B36" s="4"/>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">확대·축소 후 이미지와 박스 좌표가 일치하는 화면 동작을 확인한다.</t>
+          <t xml:space="preserve">금액 현황에서 합계·부가세·원가구분·불일치를 확인한다.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">스캔 문서·zoom 50/100/200%</t>
+          <t xml:space="preserve">검토 완료 항목</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 배율에서 박스가 같은 문자를 감싼다.</t>
+          <t xml:space="preserve">승인·수정 승인만 정확히 집계된다.</t>
         </is>
       </c>
       <c r="G36" s="3"/>
@@ -1079,22 +1091,22 @@
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스 생성·분석 제외·복원 후 본문 재조립을 확인한다.</t>
+          <t xml:space="preserve">출처 파일·원문 인용·계산식을 확인한다.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 요소 3건</t>
+          <t xml:space="preserve">수량×단가 항목</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 포함 요소만 순서대로 본문에 반영된다.</t>
+          <t xml:space="preserve">각 금액의 근거가 함께 표시된다.</t>
         </is>
       </c>
       <c r="G37" s="3"/>
@@ -1105,22 +1117,22 @@
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재OCR 결과를 사용자가 확인하기 전 원문을 덮지 않는지 확인한다.</t>
+          <t xml:space="preserve">VIEWER로 탭·직접 URL·API에 접근한다.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">선택 영역 1건</t>
+          <t xml:space="preserve">VIEWER 계정</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">확인 전 기존 값 유지, 확인 후 새 값 반영이다.</t>
+          <t xml:space="preserve">금액 현황은 차단되고 정책 예외인 선례 조회만 허용된다.</t>
         </is>
       </c>
       <c r="G38" s="3"/>
@@ -1131,22 +1143,22 @@
       <c r="B39" s="4"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수 완료가 확정 텍스트 저장과 재청킹 enqueue를 연결하는 API 동작을 확인한다.</t>
+          <t xml:space="preserve">분석 완료 후 페이지 이동 없이 현황을 확인한다.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 완료 문서</t>
+          <t xml:space="preserve">COMPLETED job</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">확정 리비전 저장 뒤 build_chunks 작업이 큐에 등록된다.</t>
+          <t xml:space="preserve">금액·대시보드·산출물 cache가 새 값으로 갱신된다.</t>
         </is>
       </c>
       <c r="G39" s="3"/>
@@ -1156,7 +1168,7 @@
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI·결정·일정</t>
+          <t xml:space="preserve">금액 재분석·유효 결과 전환</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1166,17 +1178,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">형식이 틀린 요약을 raw text로 저장하지 않는지 확인한다.</t>
+          <t xml:space="preserve">완료된 기존 금액 snapshot의 합계를 기록한다.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">깨진 JSON 응답</t>
+          <t xml:space="preserve">분석 A 전체 검토 완료</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI_INVALID_RESPONSE이며 결과를 저장하지 않는다.</t>
+          <t xml:space="preserve">기준 합계가 표시된다.</t>
         </is>
       </c>
       <c r="G40" s="3"/>
@@ -1192,17 +1204,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문에 없는 인용을 가진 요약 전체를 실패시키는지 확인한다.</t>
+          <t xml:space="preserve">같은 문서를 재분석하고 신규 항목 한 건만 승인한다.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">조작된 source_quote</t>
+          <t xml:space="preserve">분석 B 일부 검토</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">무근거 요약이 저장되지 않는다.</t>
+          <t xml:space="preserve">기존 완료 합계를 유지한다.</t>
         </is>
       </c>
       <c r="G41" s="3"/>
@@ -1218,17 +1230,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 날짜가 없으면 모델을 호출하지 않는지 확인한다.</t>
+          <t xml:space="preserve">나머지 신규 항목을 승인·거절해 검토를 끝낸다.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">날짜 없는 본문</t>
+          <t xml:space="preserve">분석 B 전체 검토</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 일정 결과이며 모델 호출 0회다.</t>
+          <t xml:space="preserve">분석 B snapshot으로 한 번에 전환된다.</t>
         </is>
       </c>
       <c r="G42" s="3"/>
@@ -1244,17 +1256,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">후보 목록 밖 날짜 ID를 선택할 수 없는지 확인한다.</t>
+          <t xml:space="preserve">신규 snapshot을 전부 거절한다.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">존재하지 않는 date ID</t>
+          <t xml:space="preserve">분석 C 전체 거절</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI_INVALID_RESPONSE다.</t>
+          <t xml:space="preserve">승인 금액 0건으로 전환된다.</t>
         </is>
       </c>
       <c r="G43" s="3"/>
@@ -1270,17 +1282,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 범위 7종 코드만 허용하는지 확인한다.</t>
+          <t xml:space="preserve">다른 프로젝트에도 같은 문서명·금액을 둔다.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7종 정상 코드</t>
+          <t xml:space="preserve">프로젝트 2개</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 코드가 계약 스키마를 통과한다.</t>
+          <t xml:space="preserve">서로의 집계가 섞이지 않는다.</t>
         </is>
       </c>
       <c r="G44" s="3"/>
@@ -1288,25 +1300,29 @@
     </row>
     <row r="45" ht="38" customHeight="1">
       <c r="A45" s="3"/>
-      <c r="B45" s="4"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하이브리드 검색·원문 이동</t>
+        </is>
+      </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker 시작 전에 원문이 바뀌면 모델을 호출하지 않는지 확인한다.</t>
+          <t xml:space="preserve">고유 문서번호로 키워드 검색한다.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enqueue 후 text_version 변경</t>
+          <t xml:space="preserve">고유번호</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYSIS_SOURCE_CHANGED이며 호출 0회다.</t>
+          <t xml:space="preserve">정확 문자열 결과와 match 위치가 표시된다.</t>
         </is>
       </c>
       <c r="G45" s="3"/>
@@ -1317,22 +1333,22 @@
       <c r="B46" s="4"/>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 분석기 실패 시 성공 결과를 저장하고 job을 PARTIAL로 만드는지 확인한다.</t>
+          <t xml:space="preserve">의미 질의로 검색한다.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성공 분석기+실패 분석기</t>
+          <t xml:space="preserve">계약 해지 조건</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성공 결과는 저장되고 상태는 PARTIAL이다.</t>
+          <t xml:space="preserve">관련 의미 청크가 상위에 나온다.</t>
         </is>
       </c>
       <c r="G46" s="3"/>
@@ -1343,22 +1359,22 @@
       <c r="B47" s="4"/>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 결정의 승인·수정·거절·취소 상태 전이를 API 수준에서 확인한다.</t>
+          <t xml:space="preserve">하이브리드 검색과 reranker 순서를 확인한다.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정 후보 4건</t>
+          <t xml:space="preserve">키워드·의미 혼합 질의</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 review_decision·결정자·시각이 정확히 저장된다.</t>
+          <t xml:space="preserve">양쪽 결과가 융합·재순위된다.</t>
         </is>
       </c>
       <c r="G47" s="3"/>
@@ -1369,22 +1385,22 @@
       <c r="B48" s="4"/>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 일정의 승인·수정·거절·취소 상태 전이를 API 수준에서 확인한다.</t>
+          <t xml:space="preserve">근거를 눌러 원문으로 이동한다.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일정 후보 4건</t>
+          <t xml:space="preserve">검색 결과 1건</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 상태만 하류 집계에 포함된다.</t>
+          <t xml:space="preserve">해당 문서·인용 위치가 확인된다.</t>
         </is>
       </c>
       <c r="G48" s="3"/>
@@ -1395,22 +1411,22 @@
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기 추가·PARTIAL·FAILED 상태를 화면이 동적으로 표시하는 동작을 확인한다.</t>
+          <t xml:space="preserve">접근 권한이 없는 프로젝트의 검색 화면을 연다.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPLETED·PARTIAL·FAILED job</t>
+          <t xml:space="preserve">비멤버 계정</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기 수를 하드코딩하지 않고 상태를 표시한다.</t>
+          <t xml:space="preserve">검색 결과가 노출되지 않고 접근 제한 안내가 표시된다.</t>
         </is>
       </c>
       <c r="G49" s="3"/>
@@ -1418,25 +1434,29 @@
     </row>
     <row r="50" ht="38" customHeight="1">
       <c r="A50" s="3"/>
-      <c r="B50" s="4"/>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근거 기반 질의응답</t>
+        </is>
+      </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">실제 Docker worker에서 Ollama 구조화 출력과 오류 코드를 통합 확인한다.</t>
+          <t xml:space="preserve">근거가 있는 질문을 하고 evidence를 연다.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 JSON·schema 오류·연결 실패</t>
+          <t xml:space="preserve">본문에 답이 있는 질문</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 저장, schema 오류 AI_INVALID_RESPONSE, 연결 실패 AI_PROVIDER_ERROR다.</t>
+          <t xml:space="preserve">답변 인용이 실제 청크와 일치한다.</t>
         </is>
       </c>
       <c r="G50" s="3"/>
@@ -1444,29 +1464,25 @@
     </row>
     <row r="51" ht="38" customHeight="1">
       <c r="A51" s="3"/>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">액션 아이템·태스크</t>
-        </is>
-      </c>
+      <c r="B51" s="4"/>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약 계열 문서에서만 기본 액션 분석기가 도는지 확인한다.</t>
+          <t xml:space="preserve">검색 결과가 없는 질문을 한다.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약·회의록 문서</t>
+          <t xml:space="preserve">문서 밖 질문</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에서 실행되고 비대상 유형에서는 호출하지 않는다.</t>
+          <t xml:space="preserve">LLM 호출 없이 근거 없음으로 답한다.</t>
         </is>
       </c>
       <c r="G51" s="3"/>
@@ -1477,22 +1493,22 @@
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 후보에 근거한 항목만 결과로 반환하는지 확인한다.</t>
+          <t xml:space="preserve">근거 연결이 잘못된 답변을 확인한다.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">실제 후보+모델 조작 후보</t>
+          <t xml:space="preserve">허용 범위 밖 근거가 포함된 응답</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">실제 후보만 남는다.</t>
+          <t xml:space="preserve">잘못된 근거 답변이 화면에 표시되지 않는다.</t>
         </is>
       </c>
       <c r="G52" s="3"/>
@@ -1503,22 +1519,22 @@
       <c r="B53" s="4"/>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">후보가 없으면 모델을 호출하지 않는지 확인한다.</t>
+          <t xml:space="preserve">answerable=false 응답의 문구를 확인한다.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">액션 문장 없는 본문</t>
+          <t xml:space="preserve">근거 없는 응답</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 결과와 모델 호출 0회다.</t>
+          <t xml:space="preserve">단정적 숫자·사실을 말하지 않는다.</t>
         </is>
       </c>
       <c r="G53" s="3"/>
@@ -1529,22 +1545,22 @@
       <c r="B54" s="4"/>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 분석기의 미검토 후보만 재분석 결과로 교체하는지 확인한다.</t>
+          <t xml:space="preserve">원문에 없는 숫자를 질문한다.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존 PENDING·APPROVED 후보</t>
+          <t xml:space="preserve">근거가 없는 숫자 질문</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING만 교체되고 검토 완료 후보는 보존된다.</t>
+          <t xml:space="preserve">근거 없는 숫자를 단정하지 않고 확인할 자료가 없다고 안내한다.</t>
         </is>
       </c>
       <c r="G54" s="3"/>
@@ -1552,25 +1568,29 @@
     </row>
     <row r="55" ht="38" customHeight="1">
       <c r="A55" s="3"/>
-      <c r="B55" s="4"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인건비 계산 질의</t>
+        </is>
+      </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 트랜잭션이 AI_APPROVED 태스크를 정확히 한 건 만드는 API 동작을 확인한다.</t>
+          <t xml:space="preserve">명시 인월 질문을 한다.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 제안 1건</t>
+          <t xml:space="preserve">9,500,000원×6인월</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 상태와 Task 생성이 함께 커밋된다.</t>
+          <t xml:space="preserve">57,000,000원과 근거가 표시된다.</t>
         </is>
       </c>
       <c r="G55" s="3"/>
@@ -1581,22 +1601,22 @@
       <c r="B56" s="4"/>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">거절 후 보드에 나타나지 않고 거절 목록과 결정자 정보가 남는지 확인한다.</t>
+          <t xml:space="preserve">인원·개월·투입률 질문을 한다.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 제안 1건</t>
+          <t xml:space="preserve">9,500,000원×2명×3개월×50%</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Task는 생기지 않고 REJECTED 이력이 표시된다.</t>
+          <t xml:space="preserve">28,500,000원과 유효 3인월이 표시된다.</t>
         </is>
       </c>
       <c r="G56" s="3"/>
@@ -1604,29 +1624,25 @@
     </row>
     <row r="57" ht="38" customHeight="1">
       <c r="A57" s="3"/>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액</t>
-        </is>
-      </c>
+      <c r="B57" s="4"/>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 JSON을 정규화해 계약 스키마로 반환하는지 확인한다.</t>
+          <t xml:space="preserve">복수 기술자에 서로 다른 인월을 질문한다.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문자열 숫자가 포함된 정상 JSON</t>
+          <t xml:space="preserve">기술자 2명·인월 2개</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정규화된 AmountExtractionOut이다.</t>
+          <t xml:space="preserve">이름별 올바른 단가와 수량을 매핑한다.</t>
         </is>
       </c>
       <c r="G57" s="3"/>
@@ -1637,22 +1653,22 @@
       <c r="B58" s="4"/>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">코드펜스·잘못된 root·NaN·Infinity를 거부하는지 확인한다.</t>
+          <t xml:space="preserve">모호·범위 밖 투입률을 질문한다.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비표준 JSON 세트</t>
+          <t xml:space="preserve">복수 50/70%, 120%</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모두 AI_INVALID_RESPONSE다.</t>
+          <t xml:space="preserve">임의 계산하지 않고 명확화를 요청한다.</t>
         </is>
       </c>
       <c r="G58" s="3"/>
@@ -1660,25 +1676,29 @@
     </row>
     <row r="59" ht="38" customHeight="1">
       <c r="A59" s="3"/>
-      <c r="B59" s="4"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드</t>
+        </is>
+      </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">허용하지 않은 필드가 있으면 거부하는지 확인한다.</t>
+          <t xml:space="preserve">산출물 화면에서 프로젝트 현황을 선택하고 기간 없이 건수·본문을 미리 본다.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown 필드 포함 JSON</t>
+          <t xml:space="preserve">PROJECT_STATUS</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI_INVALID_RESPONSE다.</t>
+          <t xml:space="preserve">기간을 요구하지 않고 현재 자료를 보여준다.</t>
         </is>
       </c>
       <c r="G59" s="3"/>
@@ -1689,22 +1709,22 @@
       <c r="B60" s="4"/>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">음수·정규화 불가능 숫자를 null로 숨기지 않는지 확인한다.</t>
+          <t xml:space="preserve">본문 상단 다섯 절을 확인한다.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">음수·깨진 숫자</t>
+          <t xml:space="preserve">프로젝트·태스크·일정 자료</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI_INVALID_RESPONSE다.</t>
+          <t xml:space="preserve">프로젝트 기본 정보·진행 상태 요약·주요 성과·일정 이슈·향후 계획이 DB 값으로 생성된다.</t>
         </is>
       </c>
       <c r="G60" s="3"/>
@@ -1715,22 +1735,22 @@
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검증된 값과 source revision을 PENDING 행으로 저장하는지 확인한다.</t>
+          <t xml:space="preserve">상세 표의 문서·태스크·결정·일정·금액을 확인한다.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 AmountExtractionOut</t>
+          <t xml:space="preserve">승인·대기·거절 자료 혼합</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 항목이 PENDING이며 revision이 기록된다.</t>
+          <t xml:space="preserve">승인 계약과 유효 snapshot에 맞는 현재 자료만 포함된다.</t>
         </is>
       </c>
       <c r="G61" s="3"/>
@@ -1741,22 +1761,22 @@
       <c r="B62" s="4"/>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재분석이 미검토 항목만 교체하고 검토 이력을 보존하는지 확인한다.</t>
+          <t xml:space="preserve">MD·HTML·XLSX·PDF로 프로젝트 현황을 생성한다.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING·APPROVED 혼합</t>
+          <t xml:space="preserve">네 출력 형식</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING만 교체된다.</t>
+          <t xml:space="preserve">네 형식 모두 같은 절과 자료를 가진 파일이 생성된다.</t>
         </is>
       </c>
       <c r="G62" s="3"/>
@@ -1767,22 +1787,22 @@
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">부가세 항목을 item_total에서 제외하는지 확인한다.</t>
+          <t xml:space="preserve">이력에서 파일을 다시 내려받고 VIEWER로도 다운로드한다.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">공급가액+VAT</t>
+          <t xml:space="preserve">생성된 산출물 ID</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">item_total은 공급가액만 포함한다.</t>
+          <t xml:space="preserve">제목 기반 파일명으로 다운로드되며 VIEWER 조회는 허용된다.</t>
         </is>
       </c>
       <c r="G63" s="3"/>
@@ -1793,22 +1813,22 @@
       <c r="B64" s="4"/>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 금액과 계산값이 다르면 고치지 않고 차이를 보고하는지 확인한다.</t>
+          <t xml:space="preserve">원천 자료 추가와 201건 이상 절을 확인한다.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수량×단가≠기재금액</t>
+          <t xml:space="preserve">생성 후 문서 추가·항목 201건</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mismatch가 반환되고 원값은 유지된다.</t>
+          <t xml:space="preserve">stale가 표시되고 200건 상한이면 생략 건수가 사용자에게 안내된다.</t>
         </is>
       </c>
       <c r="G64" s="3"/>
@@ -1816,25 +1836,29 @@
     </row>
     <row r="65" ht="38" customHeight="1">
       <c r="A65" s="3"/>
-      <c r="B65" s="4"/>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리 실패·재시도·오류 안내</t>
+        </is>
+      </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서로 다른 통화가 섞이면 집계를 거부하는지 확인한다.</t>
+          <t xml:space="preserve">문서를 업로드하고 처리 상태를 확인한다.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KRW·USD 문서</t>
+          <t xml:space="preserve">정상 문서</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">혼합 통화 오류가 발생한다.</t>
+          <t xml:space="preserve">처리 중 상태가 화면에 표시된다.</t>
         </is>
       </c>
       <c r="G65" s="3"/>
@@ -1845,22 +1869,22 @@
       <c r="B66" s="4"/>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">부분 승인 중에는 이전 완료 스냅샷을 유지하는지 확인한다.</t>
+          <t xml:space="preserve">처리 실패 문서의 상태와 사유를 확인한다.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이전 완료+신규 일부 승인</t>
+          <t xml:space="preserve">추출 실패 문서</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">합계가 급락하지 않고 전체 검토 후 전환된다.</t>
+          <t xml:space="preserve">실패 상태와 사용자가 이해할 수 있는 사유가 표시된다.</t>
         </is>
       </c>
       <c r="G66" s="3"/>
@@ -1871,22 +1895,22 @@
       <c r="B67" s="4"/>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서마다 유효 분석을 고르고 다른 프로젝트를 섞지 않는지 확인한다.</t>
+          <t xml:space="preserve">실패 문서의 재시도를 실행한다.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 2개·재분석 다건</t>
+          <t xml:space="preserve">재시도 가능한 문서</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">요청 프로젝트의 유효 행만 반환된다.</t>
+          <t xml:space="preserve">처리가 다시 시작되고 최종 상태로 변경된다.</t>
         </is>
       </c>
       <c r="G67" s="3"/>
@@ -1897,22 +1921,22 @@
       <c r="B68" s="4"/>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인만 집계되는지 확인한다.</t>
+          <t xml:space="preserve">처리 중 서비스 재시작 후 화면을 새로고침한다.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED·EDITED·PENDING·REJECTED</t>
+          <t xml:space="preserve">처리 중 문서</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED와 EDITED만 집계된다.</t>
+          <t xml:space="preserve">작업이 유실되지 않고 완료 또는 실패 상태로 표시된다.</t>
         </is>
       </c>
       <c r="G68" s="3"/>
@@ -1923,22 +1947,22 @@
       <c r="B69" s="4"/>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인·거절·취소와 허용 수정 필드를 API 수준에서 확인한다.</t>
+          <t xml:space="preserve">AI 연결 실패 상황에서 안내 문구를 확인한다.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 항목 4건</t>
+          <t xml:space="preserve">AI 서버 연결 실패</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태·결정자·결정시각과 수정값이 계약대로 저장된다.</t>
+          <t xml:space="preserve">AI 연결 오류 안내와 재시도 방법이 표시된다.</t>
         </is>
       </c>
       <c r="G69" s="3"/>
@@ -1949,971 +1973,42 @@
       <c r="B70" s="4"/>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER 탭·직접 URL·API 차단과 분석 완료 후 금액 캐시 무효화를 확인한다.</t>
+          <t xml:space="preserve">AI 응답 형식 오류 상황에서 안내 문구를 확인한다.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OWNER·EDITOR·VIEWER 및 완료 job</t>
+          <t xml:space="preserve">형식이 잘못된 AI 응답</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER는 제한되고 OWNER·EDITOR 화면은 새 집계로 갱신된다.</t>
+          <t xml:space="preserve">분석 실패 안내가 표시되고 원문 응답은 노출되지 않는다.</t>
         </is>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" ht="38" customHeight="1">
-      <c r="A71" s="3"/>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색·RAG·질의응답</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기존 문단·표 구조를 존중해 청크를 만드는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문단+표 구조 요소</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">표 행이 깨지지 않고 구조 경계가 유지된다.</t>
-        </is>
-      </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="2"/>
-    </row>
-    <row r="72" ht="38" customHeight="1">
-      <c r="A72" s="3"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조립 결과가 예산을 넘지 않는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">긴 청크 다건·budget 4000</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최종 컨텍스트가 4000 token 이하다.</t>
-        </is>
-      </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="2"/>
-    </row>
-    <row r="73" ht="38" customHeight="1">
-      <c r="A73" s="3"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">벡터·키워드 양쪽 순위를 합산하는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">양쪽에 등장하는 같은 chunk</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">양쪽 점수 합이 적용된다.</t>
-        </is>
-      </c>
-      <c r="G73" s="3"/>
-      <c r="H73" s="2"/>
-    </row>
-    <row r="74" ht="38" customHeight="1">
-      <c r="A74" s="3"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하이브리드 경로가 실제 reranker를 호출하는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">후보 다건</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reranker 결과 순서가 반환된다.</t>
-        </is>
-      </c>
-      <c r="G74" s="3"/>
-      <c r="H74" s="2"/>
-    </row>
-    <row r="75" ht="38" customHeight="1">
-      <c r="A75" s="3"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reranker 실패 시 융합 순서로 검색을 계속하는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reranker 예외</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색 전체가 실패하지 않고 결과를 반환한다.</t>
-        </is>
-      </c>
-      <c r="G75" s="3"/>
-      <c r="H75" s="2"/>
-    </row>
-    <row r="76" ht="38" customHeight="1">
-      <c r="A76" s="3"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사용자 %·_ 문자가 전체 일치로 확장되지 않는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색어 %_</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와일드카드가 escape된다.</t>
-        </is>
-      </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="2"/>
-    </row>
-    <row r="77" ht="38" customHeight="1">
-      <c r="A77" s="3"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비멤버가 project_id를 지정하면 404인지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비멤버 project_id</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">존재를 숨기는 404다.</t>
-        </is>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="2"/>
-    </row>
-    <row r="78" ht="38" customHeight="1">
-      <c r="A78" s="3"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조립하지 않은 evidence ID를 모델이 참조할 수 없는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">범위 밖 evidence ID</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI_INVALID_RESPONSE 또는 보류 응답이다.</t>
-        </is>
-      </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="2"/>
-    </row>
-    <row r="79" ht="38" customHeight="1">
-      <c r="A79" s="3"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색 결과가 없으면 모델을 호출하지 않는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색 0건</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">근거 없음 응답과 모델 호출 0회다.</t>
-        </is>
-      </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="2"/>
-    </row>
-    <row r="80" ht="38" customHeight="1">
-      <c r="A80" s="3"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">확정 평가셋과 동일 지표 정의로 R@1을 측정한다.</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">평가셋·선정 임베딩 모델</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">accuracy@1 정의로 결과를 재현하고 표준 recall과 혼동하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="2"/>
-    </row>
-    <row r="81" ht="38" customHeight="1">
-      <c r="A81" s="3"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 확정 직후 worker 교체 전 낡은 청크가 검색되는 구간을 전체 흐름에서 확인한다.</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">본문 변경 직후 검색</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새 청크 반영 전에는 낡은 근거를 최신으로 표시하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G81" s="3"/>
-      <c r="H81" s="2"/>
-    </row>
-    <row r="82" ht="38" customHeight="1">
-      <c r="A82" s="3"/>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인건비 계산</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">단가×명시 인월을 LLM 없이 계산하는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">단가 9,500,000원·6인월</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57,000,000원과 근거가 반환된다.</t>
-        </is>
-      </c>
-      <c r="G82" s="3"/>
-      <c r="H82" s="2"/>
-    </row>
-    <row r="83" ht="38" customHeight="1">
-      <c r="A83" s="3"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서로 다른 기술자별 인월을 각 단가에 매핑하는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기술자 2명·서로 다른 인월</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">각 항목별 계산 결과가 분리된다.</t>
-        </is>
-      </c>
-      <c r="G83" s="3"/>
-      <c r="H83" s="2"/>
-    </row>
-    <row r="84" ht="38" customHeight="1">
-      <c r="A84" s="3"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">단가×인원×개월×50% 계산의 전용 회귀 동작을 확인한다.</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9,500,000원×2명×3개월×50%</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28,500,000원이며 57,000,000원으로 계산하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G84" s="3"/>
-      <c r="H84" s="2"/>
-    </row>
-    <row r="85" ht="38" customHeight="1">
-      <c r="A85" s="3"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">복수 인원·기간·투입률이 항목에 명확히 연결되지 않으면 계산을 보류한다.</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기술자 2명·인월 2개·이름 매핑 없음</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임의 배분하지 않고 명확화 질문을 반환한다.</t>
-        </is>
-      </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="2"/>
-    </row>
-    <row r="86" ht="38" customHeight="1">
-      <c r="A86" s="3"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%·100%·100% 초과와 소수 인월의 반올림 정책을 확인한다.</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%, 100%, 120%, 1.5인월</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유효 범위만 계산하고 원 단위 반올림이 일관된다.</t>
-        </is>
-      </c>
-      <c r="G86" s="3"/>
-      <c r="H86" s="2"/>
-    </row>
-    <row r="87" ht="38" customHeight="1">
-      <c r="A87" s="3"/>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출물</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기간을 무시하고 현재 자료 전체를 세는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기간 파라미터+현재 자료</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">period는 None이며 현재 건수가 반환된다.</t>
-        </is>
-      </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="2"/>
-    </row>
-    <row r="88" ht="38" customHeight="1">
-      <c r="A88" s="3"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LLM 없이 기본정보·진행상태·주요성과·일정이슈·향후계획을 만드는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트·태스크·일정 자료</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다섯 절과 현재 자료 표가 생성된다.</t>
-        </is>
-      </c>
-      <c r="G88" s="3"/>
-      <c r="H88" s="2"/>
-    </row>
-    <row r="89" ht="38" customHeight="1">
-      <c r="A89" s="3"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DB 재료가 렌더링 본문에 포함되는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서·태스크·결정·일정·금액</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">각 실제 행이 본문에 표시된다.</t>
-        </is>
-      </c>
-      <c r="G89" s="3"/>
-      <c r="H89" s="2"/>
-    </row>
-    <row r="90" ht="38" customHeight="1">
-      <c r="A90" s="3"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MD와 HTML이 같은 절을 갖는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">같은 DeliverableMaterials</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">절 제목과 개수가 같다.</t>
-        </is>
-      </c>
-      <c r="G90" s="3"/>
-      <c r="H90" s="2"/>
-    </row>
-    <row r="91" ht="38" customHeight="1">
-      <c r="A91" s="3"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XLSX 금액이 문자열이 아닌 숫자 셀인지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 항목 1건</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 셀 데이터형이 숫자다.</t>
-        </is>
-      </c>
-      <c r="G91" s="3"/>
-      <c r="H91" s="2"/>
-    </row>
-    <row r="92" ht="38" customHeight="1">
-      <c r="A92" s="3"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">원천 자료가 늘면 stale로 표시하는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생성 snapshot 뒤 문서 1건 추가</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">is_stale과 증가 항목이 반환된다.</t>
-        </is>
-      </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="2"/>
-    </row>
-    <row r="93" ht="38" customHeight="1">
-      <c r="A93" s="3"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다른 프로젝트의 산출물을 열 수 없는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 A 요청·B 산출물 ID</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DELIVERABLE_NOT_FOUND다.</t>
-        </is>
-      </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="2"/>
-    </row>
-    <row r="94" ht="38" customHeight="1">
-      <c r="A94" s="3"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">count와 list가 같은 유효 금액 snapshot을 사용하는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재분석·부분 승인 금액</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미리보기 건수와 본문 항목 수가 같은 규칙을 쓴다.</t>
-        </is>
-      </c>
-      <c r="G94" s="3"/>
-      <c r="H94" s="2"/>
-    </row>
-    <row r="95" ht="38" customHeight="1">
-      <c r="A95" s="3"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화면에서 PROJECT_STATUS를 선택해 네 형식 생성·이력·다운로드를 확인한다.</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MD·HTML·XLSX·PDF</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네 파일이 생성되고 제목 파일명으로 재다운로드된다.</t>
-        </is>
-      </c>
-      <c r="G95" s="3"/>
-      <c r="H95" s="2"/>
-    </row>
-    <row r="96" ht="38" customHeight="1">
-      <c r="A96" s="3"/>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오류·request_id·worker</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모든 handler가 code·message·request_id 같은 키를 반환하는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">404·405·409·422</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오류 응답 키가 동일하다.</t>
-        </is>
-      </c>
-      <c r="G96" s="3"/>
-      <c r="H96" s="2"/>
-    </row>
-    <row r="97" ht="38" customHeight="1">
-      <c r="A97" s="3"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">middleware를 거치지 않은 오류도 request_id를 갖는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">middleware 없는 request</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fallback request_id가 응답에 포함된다.</t>
-        </is>
-      </c>
-      <c r="G97" s="3"/>
-      <c r="H97" s="2"/>
-    </row>
-    <row r="98" ht="38" customHeight="1">
-      <c r="A98" s="3"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 재처리 API의 request_id가 worker 로그까지 이어지는 동작을 확인한다.</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X-Request-ID 고정값</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API·queue message·worker log에서 같은 값이 보인다.</t>
-        </is>
-      </c>
-      <c r="G98" s="3"/>
-      <c r="H98" s="2"/>
-    </row>
-    <row r="99" ht="38" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ollama 연결 실패와 schema 실패가 서로 다른 오류 코드인지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">연결 거부·malformed JSON</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">각각 AI_PROVIDER_ERROR·AI_INVALID_RESPONSE다.</t>
-        </is>
-      </c>
-      <c r="G99" s="3"/>
-      <c r="H99" s="2"/>
-    </row>
-    <row r="100" ht="38" customHeight="1">
-      <c r="A100" s="3"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">처리 중 worker 종료·재시작 뒤 작업이 유실되지 않는 연동을 확인한다.</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실행 중 강제 종료</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재시작 후 재수행 또는 명시적 실패로 수렴한다.</t>
-        </is>
-      </c>
-      <c r="G100" s="3"/>
-      <c r="H100" s="2"/>
-    </row>
-    <row r="101" ht="38" customHeight="1">
-      <c r="A101" s="3"/>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 데이터 격리</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유효 snapshot 조회가 다른 프로젝트 행을 섞지 않는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동일 document id 맥락의 프로젝트 2개</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요청 프로젝트 금액만 반환된다.</t>
-        </is>
-      </c>
-      <c r="G101" s="3"/>
-      <c r="H101" s="2"/>
-    </row>
-    <row r="102" ht="38" customHeight="1">
-      <c r="A102" s="3"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서와 청크가 같은 프로젝트일 때만 컨텍스트로 쓰는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다른 프로젝트 document·chunk</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">교차 프로젝트 근거가 제외된다.</t>
-        </is>
-      </c>
-      <c r="G102" s="3"/>
-      <c r="H102" s="2"/>
-    </row>
-    <row r="103" ht="38" customHeight="1">
-      <c r="A103" s="3"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">파일 중복 검사가 프로젝트 범위를 넘지 않는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">같은 hash·프로젝트 2개</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">각 프로젝트에 한 번씩 업로드할 수 있다.</t>
-        </is>
-      </c>
-      <c r="G103" s="3"/>
-      <c r="H103" s="2"/>
-    </row>
-    <row r="104" ht="38" customHeight="1">
-      <c r="A104" s="3"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서·OCR·분석·금액·산출물 ID를 다른 프로젝트 URL에 넣는 API 행렬 동작을 확인한다.</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 A 사용자·B 리소스 ID</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모든 경로가 404이며 존재 여부를 노출하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G104" s="3"/>
-      <c r="H104" s="2"/>
-    </row>
-    <row r="105" ht="38" customHeight="1">
-      <c r="A105" s="3"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멤버 제외 직후 열린 화면과 직접 API가 모두 차단되는지 확인한다.</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제외 전 로그인 세션</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기존 토큰이어도 프로젝트 접근이 즉시 차단된다.</t>
-        </is>
-      </c>
-      <c r="G105" s="3"/>
-      <c r="H105" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="B8:B16"/>
-    <mergeCell ref="B17:B26"/>
-    <mergeCell ref="B27:B39"/>
-    <mergeCell ref="B40:B50"/>
-    <mergeCell ref="B51:B56"/>
-    <mergeCell ref="B57:B70"/>
-    <mergeCell ref="B71:B81"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="B87:B95"/>
-    <mergeCell ref="B96:B100"/>
-    <mergeCell ref="B101:B105"/>
+  <mergeCells count="13">
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="B59:B64"/>
+    <mergeCell ref="B65:B70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>

--- a/산출물/단위테스트명세서.xlsx
+++ b/산출물/단위테스트명세서.xlsx
@@ -93,7 +93,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -420,7 +420,7 @@
       <c r="A12" s="3"/>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">다중 문서 업로드·목록 조회</t>
+          <t xml:space="preserve">월간 캘린더 조회</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -430,17 +430,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지원 파일 5종을 다중 업로드한다.</t>
+          <t xml:space="preserve">대시보드 캘린더에서 이전 달·다음 달·오늘로 이동한다.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDF·DOCX·HWPX·JPG·PNG</t>
+          <t xml:space="preserve">태스크 마감일·승인 일정</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 문서 ID가 즉시 반환되고 PENDING이다.</t>
+          <t xml:space="preserve">선택한 월의 일정과 기한이 날짜에 맞게 표시된다.</t>
         </is>
       </c>
       <c r="G12" s="3"/>
@@ -456,17 +456,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">형식·크기·빈 파일·중복·경로 조작 오류를 유도한다.</t>
+          <t xml:space="preserve">여러 날짜에 걸친 일정과 기한 일정을 확인한다.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오류 파일 세트</t>
+          <t xml:space="preserve">기간 일정·마감 일정</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효 파일만 저장되고 원인별 오류다.</t>
+          <t xml:space="preserve">기간 일정은 해당 날짜에 이어지고 기한은 종료일에 표시된다.</t>
         </is>
       </c>
       <c r="G13" s="3"/>
@@ -482,17 +482,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 처리 상태가 완료될 때까지 확인한다.</t>
+          <t xml:space="preserve">캘린더의 태스크를 선택하고 마감 임박 건수를 확인한다.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">텍스트·스캔 문서</t>
+          <t xml:space="preserve">7일 이내 미완료 태스크</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출 방식과 EXTRACTED 상태가 기록된다.</t>
+          <t xml:space="preserve">해당 태스크가 보드에서 강조되고 마감 임박 건수가 최신 상태로 표시된다.</t>
         </is>
       </c>
       <c r="G14" s="3"/>
@@ -500,25 +500,29 @@
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="A15" s="3"/>
-      <c r="B15" s="4"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다중 문서 업로드·목록 조회</t>
+        </is>
+      </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 건을 실패시킨 뒤 재처리한다.</t>
+          <t xml:space="preserve">지원 파일 5종을 다중 업로드한다.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출기 실패 문서</t>
+          <t xml:space="preserve">PDF·DOCX·HWPX·JPG·PNG</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오류가 보이고 재처리 후 완료 또는 명시적 실패다.</t>
+          <t xml:space="preserve">각 문서 ID가 즉시 반환되고 PENDING이다.</t>
         </is>
       </c>
       <c r="G15" s="3"/>
@@ -529,22 +533,22 @@
       <c r="B16" s="4"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서를 21건으로 만들고 2페이지로 이동한다.</t>
+          <t xml:space="preserve">형식·크기·빈 파일·중복·경로 조작 오류를 유도한다.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21건·size 20</t>
+          <t xml:space="preserve">오류 파일 세트</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1페이지 20건, 2페이지 1건이며 URL page가 유지된다.</t>
+          <t xml:space="preserve">유효 파일만 저장되고 원인별 오류다.</t>
         </is>
       </c>
       <c r="G16" s="3"/>
@@ -555,22 +559,22 @@
       <c r="B17" s="4"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">필터를 변경하고 새로고침한다.</t>
+          <t xml:space="preserve">문서 처리 상태가 완료될 때까지 확인한다.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2페이지에서 유형 필터</t>
+          <t xml:space="preserve">텍스트·스캔 문서</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">page가 초기화되고 필터 상태가 일관된다.</t>
+          <t xml:space="preserve">추출 방식과 EXTRACTED 상태가 기록된다.</t>
         </is>
       </c>
       <c r="G17" s="3"/>
@@ -578,29 +582,25 @@
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="3"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 검수·최신 검색 반영</t>
-        </is>
-      </c>
+      <c r="B18" s="4"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수 화면에서 이미지·박스·신뢰도를 확인하고 확대한다.</t>
+          <t xml:space="preserve">한 건을 실패시킨 뒤 재처리한다.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">스캔 문서</t>
+          <t xml:space="preserve">추출기 실패 문서</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 배율에서 박스와 문자가 일치한다.</t>
+          <t xml:space="preserve">오류가 보이고 재처리 후 완료 또는 명시적 실패다.</t>
         </is>
       </c>
       <c r="G18" s="3"/>
@@ -611,22 +611,22 @@
       <c r="B19" s="4"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">텍스트·좌표·단락·읽기 순서를 수정한다.</t>
+          <t xml:space="preserve">문서를 21건으로 만들고 2페이지로 이동한다.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오탈자·2단·표 문서</t>
+          <t xml:space="preserve">21건·size 20</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 보존, version 증가, 본문 순서가 정확하다.</t>
+          <t xml:space="preserve">1페이지 20건, 2페이지 1건이며 URL page가 유지된다.</t>
         </is>
       </c>
       <c r="G19" s="3"/>
@@ -637,22 +637,22 @@
       <c r="B20" s="4"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스를 생성·제외·복원하고 병합·분리한다.</t>
+          <t xml:space="preserve">필터를 변경하고 새로고침한다.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 요소 다건</t>
+          <t xml:space="preserve">2페이지에서 유형 필터</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 포함 요소만 확정 본문에 반영된다.</t>
+          <t xml:space="preserve">page가 초기화되고 필터 상태가 일관된다.</t>
         </is>
       </c>
       <c r="G20" s="3"/>
@@ -660,25 +660,29 @@
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 검수·최신 검색 반영</t>
+        </is>
+      </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두 세션에서 같은 요소를 수정한다.</t>
+          <t xml:space="preserve">검수 화면에서 이미지·박스·신뢰도를 확인하고 확대한다.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 version 동시 요청</t>
+          <t xml:space="preserve">스캔 문서</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나중 요청은 409이며 부분 변경이 없다.</t>
+          <t xml:space="preserve">모든 배율에서 박스와 문자가 일치한다.</t>
         </is>
       </c>
       <c r="G21" s="3"/>
@@ -689,22 +693,22 @@
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수를 완료하고 재청킹 상태를 확인한다.</t>
+          <t xml:space="preserve">텍스트·좌표·단락·읽기 순서를 수정한다.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 완료 문서</t>
+          <t xml:space="preserve">오탈자·2단·표 문서</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">확정 리비전과 재인덱싱 작업이 연결된다.</t>
+          <t xml:space="preserve">원문 보존, version 증가, 본문 순서가 정확하다.</t>
         </is>
       </c>
       <c r="G22" s="3"/>
@@ -715,22 +719,22 @@
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색에서 수정 전·후 문구를 조회한다.</t>
+          <t xml:space="preserve">A~D 박스를 병합하고 새로고침한 뒤 병합 되돌리기를 실행한다.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이전 문구·새 문구</t>
+          <t xml:space="preserve">좌표·텍스트·읽기 순서가 다른 OCR 박스 A~D</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 근거만 최신 결과로 표시된다.</t>
+          <t xml:space="preserve">병합 결과 E가 유지되고, 병합 되돌리기 후 A~D의 위치·텍스트·읽기 순서가 원래대로 복원된다.</t>
         </is>
       </c>
       <c r="G23" s="3"/>
@@ -738,29 +742,25 @@
     </row>
     <row r="24" ht="38" customHeight="1">
       <c r="A24" s="3"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결정사항·일정 분석·검토</t>
-        </is>
-      </c>
+      <c r="B24" s="4"/>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">회의록 분석을 실행하고 job 상태를 조회한다.</t>
+          <t xml:space="preserve">두 세션에서 같은 요소를 수정한다.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정·일정 포함 회의록</t>
+          <t xml:space="preserve">동일 version 동시 요청</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두 분석기가 완료되고 PENDING 후보가 생긴다.</t>
+          <t xml:space="preserve">나중 요청은 409이며 부분 변경이 없다.</t>
         </is>
       </c>
       <c r="G24" s="3"/>
@@ -771,22 +771,22 @@
       <c r="B25" s="4"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정 후보를 승인·수정 승인·거절·취소한다.</t>
+          <t xml:space="preserve">검수를 완료하고 재청킹 상태를 확인한다.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정 후보 4건</t>
+          <t xml:space="preserve">수정 완료 문서</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태·결정자·시각이 기록된다.</t>
+          <t xml:space="preserve">확정 리비전과 재인덱싱 작업이 연결된다.</t>
         </is>
       </c>
       <c r="G25" s="3"/>
@@ -797,22 +797,22 @@
       <c r="B26" s="4"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일정 후보도 같은 네 상태로 처리한다.</t>
+          <t xml:space="preserve">검색에서 수정 전·후 문구를 조회한다.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일정 후보 4건</t>
+          <t xml:space="preserve">이전 문구·새 문구</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 항목만 하류 데이터가 된다.</t>
+          <t xml:space="preserve">새 근거만 최신 결과로 표시된다.</t>
         </is>
       </c>
       <c r="G26" s="3"/>
@@ -820,25 +820,29 @@
     </row>
     <row r="27" ht="38" customHeight="1">
       <c r="A27" s="3"/>
-      <c r="B27" s="4"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">긴 문서 요약·분석 이력</t>
+        </is>
+      </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 대장과 다음 회의 안건을 미리 본다.</t>
+          <t xml:space="preserve">입력 한도를 넘는 긴 문서를 분석한다.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 결정·PENDING 도메인 결정</t>
+          <t xml:space="preserve">문서 끝부분에 고유 문장이 있는 긴 문서</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대장은 승인 결정 전체, 안건은 PENDING 결정만 포함한다.</t>
+          <t xml:space="preserve">문서 전체가 여러 구간으로 처리되고 끝부분까지 누락 없이 요약된다.</t>
         </is>
       </c>
       <c r="G27" s="3"/>
@@ -849,22 +853,22 @@
       <c r="B28" s="4"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 완료 뒤 대시보드·산출물 화면을 다시 연다.</t>
+          <t xml:space="preserve">요약에 사용된 근거 원문을 펼쳐 확인한다.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPLETED job</t>
+          <t xml:space="preserve">긴 문서 분석 결과</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 승인 대기·산출물 재료가 새로고침된다.</t>
+          <t xml:space="preserve">요약 문장이 표시된 원문 근거와 일치한다.</t>
         </is>
       </c>
       <c r="G28" s="3"/>
@@ -872,29 +876,25 @@
     </row>
     <row r="29" ht="38" customHeight="1">
       <c r="A29" s="3"/>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">액션 아이템 승인·태스크 완료</t>
-        </is>
-      </c>
+      <c r="B29" s="4"/>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약 문서를 분석해 PENDING 액션 제안을 만든다.</t>
+          <t xml:space="preserve">분석기 하나만 실패하도록 분석을 실행한다.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">명시적 수행 의무가 있는 계약서</t>
+          <t xml:space="preserve">정상 분석기와 오류 분석기</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 근거가 있는 후보만 생성된다.</t>
+          <t xml:space="preserve">부분 완료 안내와 실패 사유가 표시되고 성공 결과는 저장된다.</t>
         </is>
       </c>
       <c r="G29" s="3"/>
@@ -905,22 +905,22 @@
       <c r="B30" s="4"/>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제안 하나를 승인한다.</t>
+          <t xml:space="preserve">같은 문서를 다시 분석하고 최신·과거 결과 정보를 확인한다.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 제안</t>
+          <t xml:space="preserve">재분석 결과 2건</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI_APPROVED 태스크 한 건이 생긴다.</t>
+          <t xml:space="preserve">기존 이력이 유지되고 최신 결과의 모델·프롬프트 버전을 확인할 수 있다.</t>
         </is>
       </c>
       <c r="G30" s="3"/>
@@ -928,25 +928,29 @@
     </row>
     <row r="31" ht="38" customHeight="1">
       <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항·일정 분석·검토</t>
+        </is>
+      </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 제안을 거절한다.</t>
+          <t xml:space="preserve">회의록 분석을 실행하고 job 상태를 조회한다.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING 제안</t>
+          <t xml:space="preserve">결정·일정 포함 회의록</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보드에는 안 보이고 거절 이력에 남는다.</t>
+          <t xml:space="preserve">두 분석기가 완료되고 PENDING 후보가 생긴다.</t>
         </is>
       </c>
       <c r="G31" s="3"/>
@@ -957,22 +961,22 @@
       <c r="B32" s="4"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">태스크를 수정하고 칸반에서 DONE으로 옮긴다.</t>
+          <t xml:space="preserve">결정 후보를 승인·수정 승인·거절·취소한다.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인된 태스크</t>
+          <t xml:space="preserve">결정 후보 4건</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태와 completed_at이 기록된다.</t>
+          <t xml:space="preserve">상태·결정자·시각이 기록된다.</t>
         </is>
       </c>
       <c r="G32" s="3"/>
@@ -983,22 +987,22 @@
       <c r="B33" s="4"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 문서를 재분석한다.</t>
+          <t xml:space="preserve">일정 후보도 같은 네 상태로 처리한다.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동일 근거</t>
+          <t xml:space="preserve">일정 후보 4건</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검토 완료 후보·태스크는 중복 생성되지 않는다.</t>
+          <t xml:space="preserve">승인 항목만 하류 데이터가 된다.</t>
         </is>
       </c>
       <c r="G33" s="3"/>
@@ -1006,29 +1010,25 @@
     </row>
     <row r="34" ht="38" customHeight="1">
       <c r="A34" s="3"/>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 추출·검토·현황 갱신</t>
-        </is>
-      </c>
+      <c r="B34" s="4"/>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 분석을 실행하고 PENDING 결과를 확인한다.</t>
+          <t xml:space="preserve">결정사항 대장과 다음 회의 안건을 미리 본다.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수량·단가·총액·부가세 문서</t>
+          <t xml:space="preserve">승인 결정·PENDING 도메인 결정</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 근거와 revision을 가진 PENDING 항목이 생긴다.</t>
+          <t xml:space="preserve">대장은 승인 결정 전체, 안건은 PENDING 결정만 포함한다.</t>
         </is>
       </c>
       <c r="G34" s="3"/>
@@ -1039,22 +1039,22 @@
       <c r="B35" s="4"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인·거절·취소를 각각 수행한다.</t>
+          <t xml:space="preserve">분석 완료 뒤 대시보드·산출물 화면을 다시 연다.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">후보 4건</t>
+          <t xml:space="preserve">COMPLETED job</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검토 상태와 수정 가능 필드 계약이 지켜진다.</t>
+          <t xml:space="preserve">새 승인 대기·산출물 재료가 새로고침된다.</t>
         </is>
       </c>
       <c r="G35" s="3"/>
@@ -1062,25 +1062,29 @@
     </row>
     <row r="36" ht="38" customHeight="1">
       <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">액션 아이템 승인·태스크 완료</t>
+        </is>
+      </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 현황에서 합계·부가세·원가구분·불일치를 확인한다.</t>
+          <t xml:space="preserve">계약 문서를 분석해 PENDING 액션 제안을 만든다.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검토 완료 항목</t>
+          <t xml:space="preserve">명시적 수행 의무가 있는 계약서</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·수정 승인만 정확히 집계된다.</t>
+          <t xml:space="preserve">원문 근거가 있는 후보만 생성된다.</t>
         </is>
       </c>
       <c r="G36" s="3"/>
@@ -1091,22 +1095,22 @@
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출처 파일·원문 인용·계산식을 확인한다.</t>
+          <t xml:space="preserve">제안 하나를 승인한다.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수량×단가 항목</t>
+          <t xml:space="preserve">PENDING 제안</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">각 금액의 근거가 함께 표시된다.</t>
+          <t xml:space="preserve">AI_APPROVED 태스크 한 건이 생긴다.</t>
         </is>
       </c>
       <c r="G37" s="3"/>
@@ -1117,22 +1121,22 @@
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER로 탭·직접 URL·API에 접근한다.</t>
+          <t xml:space="preserve">다른 제안을 거절한다.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER 계정</t>
+          <t xml:space="preserve">PENDING 제안</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 현황은 차단되고 정책 예외인 선례 조회만 허용된다.</t>
+          <t xml:space="preserve">보드에는 안 보이고 거절 이력에 남는다.</t>
         </is>
       </c>
       <c r="G38" s="3"/>
@@ -1143,22 +1147,22 @@
       <c r="B39" s="4"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 완료 후 페이지 이동 없이 현황을 확인한다.</t>
+          <t xml:space="preserve">태스크를 수정하고 칸반에서 DONE으로 옮긴다.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPLETED job</t>
+          <t xml:space="preserve">승인된 태스크</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액·대시보드·산출물 cache가 새 값으로 갱신된다.</t>
+          <t xml:space="preserve">상태와 completed_at이 기록된다.</t>
         </is>
       </c>
       <c r="G39" s="3"/>
@@ -1166,29 +1170,25 @@
     </row>
     <row r="40" ht="38" customHeight="1">
       <c r="A40" s="3"/>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 재분석·유효 결과 전환</t>
-        </is>
-      </c>
+      <c r="B40" s="4"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">완료된 기존 금액 snapshot의 합계를 기록한다.</t>
+          <t xml:space="preserve">같은 문서를 재분석한다.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 A 전체 검토 완료</t>
+          <t xml:space="preserve">동일 근거</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기준 합계가 표시된다.</t>
+          <t xml:space="preserve">검토 완료 후보·태스크는 중복 생성되지 않는다.</t>
         </is>
       </c>
       <c r="G40" s="3"/>
@@ -1199,22 +1199,22 @@
       <c r="B41" s="4"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">같은 문서를 재분석하고 신규 항목 한 건만 승인한다.</t>
+          <t xml:space="preserve">VIEWER로 보드를 열고 태스크 생성·수정·삭제를 시도한다.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 B 일부 검토</t>
+          <t xml:space="preserve">VIEWER 계정</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존 완료 합계를 유지한다.</t>
+          <t xml:space="preserve">조회만 가능하고 편집 동작은 숨김 또는 권한 오류로 차단된다.</t>
         </is>
       </c>
       <c r="G41" s="3"/>
@@ -1225,22 +1225,22 @@
       <c r="B42" s="4"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나머지 신규 항목을 승인·거절해 검토를 끝낸다.</t>
+          <t xml:space="preserve">잘못된 제목·담당자·마감일로 태스크 저장을 시도한다.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 B 전체 검토</t>
+          <t xml:space="preserve">빈/공백 제목·프로젝트 밖 담당자·과거 마감일</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 B snapshot으로 한 번에 전환된다.</t>
+          <t xml:space="preserve">원인별 오류가 표시되고 태스크가 생성되거나 바뀌지 않는다.</t>
         </is>
       </c>
       <c r="G42" s="3"/>
@@ -1251,22 +1251,22 @@
       <c r="B43" s="4"/>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 snapshot을 전부 거절한다.</t>
+          <t xml:space="preserve">태스크를 DONE으로 옮겼다가 다시 진행 중으로 되돌리고 활동 기록과 대시보드를 확인한다.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 C 전체 거절</t>
+          <t xml:space="preserve">태스크 생성·수정·상태 변경·삭제</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 금액 0건으로 전환된다.</t>
+          <t xml:space="preserve">완료 시각이 생성·해제되고 변경자·내용·삭제된 제목과 열린 태스크 수가 최신 상태로 표시된다.</t>
         </is>
       </c>
       <c r="G43" s="3"/>
@@ -1274,25 +1274,29 @@
     </row>
     <row r="44" ht="38" customHeight="1">
       <c r="A44" s="3"/>
-      <c r="B44" s="4"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 추출·검토·현황 갱신</t>
+        </is>
+      </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 프로젝트에도 같은 문서명·금액을 둔다.</t>
+          <t xml:space="preserve">금액 분석을 실행하고 PENDING 결과를 확인한다.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 2개</t>
+          <t xml:space="preserve">수량·단가·총액·부가세 문서</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서로의 집계가 섞이지 않는다.</t>
+          <t xml:space="preserve">원문 근거와 revision을 가진 PENDING 항목이 생긴다.</t>
         </is>
       </c>
       <c r="G44" s="3"/>
@@ -1300,29 +1304,25 @@
     </row>
     <row r="45" ht="38" customHeight="1">
       <c r="A45" s="3"/>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하이브리드 검색·원문 이동</t>
-        </is>
-      </c>
+      <c r="B45" s="4"/>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">고유 문서번호로 키워드 검색한다.</t>
+          <t xml:space="preserve">승인·수정 승인·거절·취소를 각각 수행한다.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">고유번호</t>
+          <t xml:space="preserve">후보 4건</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확 문자열 결과와 match 위치가 표시된다.</t>
+          <t xml:space="preserve">검토 상태와 수정 가능 필드 계약이 지켜진다.</t>
         </is>
       </c>
       <c r="G45" s="3"/>
@@ -1333,22 +1333,22 @@
       <c r="B46" s="4"/>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의미 질의로 검색한다.</t>
+          <t xml:space="preserve">금액 현황에서 합계·부가세·원가구분·불일치를 확인한다.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약 해지 조건</t>
+          <t xml:space="preserve">검토 완료 항목</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">관련 의미 청크가 상위에 나온다.</t>
+          <t xml:space="preserve">승인·수정 승인만 정확히 집계된다.</t>
         </is>
       </c>
       <c r="G46" s="3"/>
@@ -1359,22 +1359,22 @@
       <c r="B47" s="4"/>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하이브리드 검색과 reranker 순서를 확인한다.</t>
+          <t xml:space="preserve">출처 파일·원문 인용·계산식을 확인한다.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">키워드·의미 혼합 질의</t>
+          <t xml:space="preserve">수량×단가 항목</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">양쪽 결과가 융합·재순위된다.</t>
+          <t xml:space="preserve">각 금액의 근거가 함께 표시된다.</t>
         </is>
       </c>
       <c r="G47" s="3"/>
@@ -1385,22 +1385,22 @@
       <c r="B48" s="4"/>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거를 눌러 원문으로 이동한다.</t>
+          <t xml:space="preserve">VIEWER로 탭·직접 URL·API에 접근한다.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 결과 1건</t>
+          <t xml:space="preserve">VIEWER 계정</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">해당 문서·인용 위치가 확인된다.</t>
+          <t xml:space="preserve">금액 현황은 차단되고 정책 예외인 선례 조회만 허용된다.</t>
         </is>
       </c>
       <c r="G48" s="3"/>
@@ -1411,22 +1411,22 @@
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">접근 권한이 없는 프로젝트의 검색 화면을 연다.</t>
+          <t xml:space="preserve">분석 완료 후 페이지 이동 없이 현황을 확인한다.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비멤버 계정</t>
+          <t xml:space="preserve">COMPLETED job</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 결과가 노출되지 않고 접근 제한 안내가 표시된다.</t>
+          <t xml:space="preserve">금액·대시보드·산출물 cache가 새 값으로 갱신된다.</t>
         </is>
       </c>
       <c r="G49" s="3"/>
@@ -1436,7 +1436,7 @@
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 기반 질의응답</t>
+          <t xml:space="preserve">금액 재분석·유효 결과 전환</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거가 있는 질문을 하고 evidence를 연다.</t>
+          <t xml:space="preserve">완료된 기존 금액 snapshot의 합계를 기록한다.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">본문에 답이 있는 질문</t>
+          <t xml:space="preserve">분석 A 전체 검토 완료</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">답변 인용이 실제 청크와 일치한다.</t>
+          <t xml:space="preserve">기준 합계가 표시된다.</t>
         </is>
       </c>
       <c r="G50" s="3"/>
@@ -1472,17 +1472,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 결과가 없는 질문을 한다.</t>
+          <t xml:space="preserve">같은 문서를 재분석하고 신규 항목 한 건만 승인한다.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 밖 질문</t>
+          <t xml:space="preserve">분석 B 일부 검토</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LLM 호출 없이 근거 없음으로 답한다.</t>
+          <t xml:space="preserve">기존 완료 합계를 유지한다.</t>
         </is>
       </c>
       <c r="G51" s="3"/>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 연결이 잘못된 답변을 확인한다.</t>
+          <t xml:space="preserve">나머지 신규 항목을 승인·거절해 검토를 끝낸다.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">허용 범위 밖 근거가 포함된 응답</t>
+          <t xml:space="preserve">분석 B 전체 검토</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">잘못된 근거 답변이 화면에 표시되지 않는다.</t>
+          <t xml:space="preserve">분석 B snapshot으로 한 번에 전환된다.</t>
         </is>
       </c>
       <c r="G52" s="3"/>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">answerable=false 응답의 문구를 확인한다.</t>
+          <t xml:space="preserve">신규 snapshot을 전부 거절한다.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 없는 응답</t>
+          <t xml:space="preserve">분석 C 전체 거절</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">단정적 숫자·사실을 말하지 않는다.</t>
+          <t xml:space="preserve">승인 금액 0건으로 전환된다.</t>
         </is>
       </c>
       <c r="G53" s="3"/>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문에 없는 숫자를 질문한다.</t>
+          <t xml:space="preserve">다른 프로젝트에도 같은 문서명·금액을 둔다.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거가 없는 숫자 질문</t>
+          <t xml:space="preserve">프로젝트 2개</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 없는 숫자를 단정하지 않고 확인할 자료가 없다고 안내한다.</t>
+          <t xml:space="preserve">서로의 집계가 섞이지 않는다.</t>
         </is>
       </c>
       <c r="G54" s="3"/>
@@ -1570,7 +1570,7 @@
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인건비 계산 질의</t>
+          <t xml:space="preserve">하이브리드 검색·원문 이동</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">명시 인월 질문을 한다.</t>
+          <t xml:space="preserve">고유 문서번호로 키워드 검색한다.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9,500,000원×6인월</t>
+          <t xml:space="preserve">고유번호</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57,000,000원과 근거가 표시된다.</t>
+          <t xml:space="preserve">정확 문자열 결과와 match 위치가 표시된다.</t>
         </is>
       </c>
       <c r="G55" s="3"/>
@@ -1606,17 +1606,17 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인원·개월·투입률 질문을 한다.</t>
+          <t xml:space="preserve">의미 질의로 검색한다.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9,500,000원×2명×3개월×50%</t>
+          <t xml:space="preserve">계약 해지 조건</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28,500,000원과 유효 3인월이 표시된다.</t>
+          <t xml:space="preserve">관련 의미 청크가 상위에 나온다.</t>
         </is>
       </c>
       <c r="G56" s="3"/>
@@ -1632,17 +1632,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">복수 기술자에 서로 다른 인월을 질문한다.</t>
+          <t xml:space="preserve">하이브리드 검색과 reranker 순서를 확인한다.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기술자 2명·인월 2개</t>
+          <t xml:space="preserve">키워드·의미 혼합 질의</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이름별 올바른 단가와 수량을 매핑한다.</t>
+          <t xml:space="preserve">양쪽 결과가 융합·재순위된다.</t>
         </is>
       </c>
       <c r="G57" s="3"/>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모호·범위 밖 투입률을 질문한다.</t>
+          <t xml:space="preserve">근거를 눌러 원문으로 이동한다.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">복수 50/70%, 120%</t>
+          <t xml:space="preserve">검색 결과 1건</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">임의 계산하지 않고 명확화를 요청한다.</t>
+          <t xml:space="preserve">해당 문서·인용 위치가 확인된다.</t>
         </is>
       </c>
       <c r="G58" s="3"/>
@@ -1676,29 +1676,25 @@
     </row>
     <row r="59" ht="38" customHeight="1">
       <c r="A59" s="3"/>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드</t>
-        </is>
-      </c>
+      <c r="B59" s="4"/>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출물 화면에서 프로젝트 현황을 선택하고 기간 없이 건수·본문을 미리 본다.</t>
+          <t xml:space="preserve">접근 권한이 없는 프로젝트의 검색 화면을 연다.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROJECT_STATUS</t>
+          <t xml:space="preserve">비멤버 계정</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기간을 요구하지 않고 현재 자료를 보여준다.</t>
+          <t xml:space="preserve">검색 결과가 노출되지 않고 접근 제한 안내가 표시된다.</t>
         </is>
       </c>
       <c r="G59" s="3"/>
@@ -1706,25 +1702,29 @@
     </row>
     <row r="60" ht="38" customHeight="1">
       <c r="A60" s="3"/>
-      <c r="B60" s="4"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근거 기반 질의응답</t>
+        </is>
+      </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">본문 상단 다섯 절을 확인한다.</t>
+          <t xml:space="preserve">근거가 있는 질문을 하고 evidence를 연다.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트·태스크·일정 자료</t>
+          <t xml:space="preserve">본문에 답이 있는 질문</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 기본 정보·진행 상태 요약·주요 성과·일정 이슈·향후 계획이 DB 값으로 생성된다.</t>
+          <t xml:space="preserve">답변 인용이 실제 청크와 일치한다.</t>
         </is>
       </c>
       <c r="G60" s="3"/>
@@ -1735,22 +1735,22 @@
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상세 표의 문서·태스크·결정·일정·금액을 확인한다.</t>
+          <t xml:space="preserve">검색 결과가 없는 질문을 한다.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인·대기·거절 자료 혼합</t>
+          <t xml:space="preserve">문서 밖 질문</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 계약과 유효 snapshot에 맞는 현재 자료만 포함된다.</t>
+          <t xml:space="preserve">LLM 호출 없이 근거 없음으로 답한다.</t>
         </is>
       </c>
       <c r="G61" s="3"/>
@@ -1761,22 +1761,22 @@
       <c r="B62" s="4"/>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MD·HTML·XLSX·PDF로 프로젝트 현황을 생성한다.</t>
+          <t xml:space="preserve">근거 연결이 잘못된 답변을 확인한다.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">네 출력 형식</t>
+          <t xml:space="preserve">허용 범위 밖 근거가 포함된 응답</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">네 형식 모두 같은 절과 자료를 가진 파일이 생성된다.</t>
+          <t xml:space="preserve">잘못된 근거 답변이 화면에 표시되지 않는다.</t>
         </is>
       </c>
       <c r="G62" s="3"/>
@@ -1787,22 +1787,22 @@
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이력에서 파일을 다시 내려받고 VIEWER로도 다운로드한다.</t>
+          <t xml:space="preserve">answerable=false 응답의 문구를 확인한다.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생성된 산출물 ID</t>
+          <t xml:space="preserve">근거 없는 응답</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 기반 파일명으로 다운로드되며 VIEWER 조회는 허용된다.</t>
+          <t xml:space="preserve">단정적 숫자·사실을 말하지 않는다.</t>
         </is>
       </c>
       <c r="G63" s="3"/>
@@ -1813,22 +1813,22 @@
       <c r="B64" s="4"/>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">원천 자료 추가와 201건 이상 절을 확인한다.</t>
+          <t xml:space="preserve">원문에 없는 숫자를 질문한다.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생성 후 문서 추가·항목 201건</t>
+          <t xml:space="preserve">근거가 없는 숫자 질문</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stale가 표시되고 200건 상한이면 생략 건수가 사용자에게 안내된다.</t>
+          <t xml:space="preserve">근거 없는 숫자를 단정하지 않고 확인할 자료가 없다고 안내한다.</t>
         </is>
       </c>
       <c r="G64" s="3"/>
@@ -1838,7 +1838,7 @@
       <c r="A65" s="3"/>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">처리 실패·재시도·오류 안내</t>
+          <t xml:space="preserve">인건비 계산 질의</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서를 업로드하고 처리 상태를 확인한다.</t>
+          <t xml:space="preserve">명시 인월 질문을 한다.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상 문서</t>
+          <t xml:space="preserve">9,500,000원×6인월</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">처리 중 상태가 화면에 표시된다.</t>
+          <t xml:space="preserve">57,000,000원과 근거가 표시된다.</t>
         </is>
       </c>
       <c r="G65" s="3"/>
@@ -1874,17 +1874,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">처리 실패 문서의 상태와 사유를 확인한다.</t>
+          <t xml:space="preserve">인원·개월·투입률 질문을 한다.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출 실패 문서</t>
+          <t xml:space="preserve">9,500,000원×2명×3개월×50%</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">실패 상태와 사용자가 이해할 수 있는 사유가 표시된다.</t>
+          <t xml:space="preserve">28,500,000원과 유효 3인월이 표시된다.</t>
         </is>
       </c>
       <c r="G66" s="3"/>
@@ -1900,17 +1900,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">실패 문서의 재시도를 실행한다.</t>
+          <t xml:space="preserve">복수 기술자에 서로 다른 인월을 질문한다.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">재시도 가능한 문서</t>
+          <t xml:space="preserve">기술자 2명·인월 2개</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">처리가 다시 시작되고 최종 상태로 변경된다.</t>
+          <t xml:space="preserve">이름별 올바른 단가와 수량을 매핑한다.</t>
         </is>
       </c>
       <c r="G67" s="3"/>
@@ -1926,17 +1926,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">처리 중 서비스 재시작 후 화면을 새로고침한다.</t>
+          <t xml:space="preserve">모호·범위 밖 투입률을 질문한다.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">처리 중 문서</t>
+          <t xml:space="preserve">복수 50/70%, 120%</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">작업이 유실되지 않고 완료 또는 실패 상태로 표시된다.</t>
+          <t xml:space="preserve">임의 계산하지 않고 명확화를 요청한다.</t>
         </is>
       </c>
       <c r="G68" s="3"/>
@@ -1944,25 +1944,29 @@
     </row>
     <row r="69" ht="38" customHeight="1">
       <c r="A69" s="3"/>
-      <c r="B69" s="4"/>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 현황 생성·이력·다운로드</t>
+        </is>
+      </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 연결 실패 상황에서 안내 문구를 확인한다.</t>
+          <t xml:space="preserve">산출물 화면에서 프로젝트 현황을 선택하고 기간 없이 건수·본문을 미리 본다.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 서버 연결 실패</t>
+          <t xml:space="preserve">PROJECT_STATUS</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 연결 오류 안내와 재시도 방법이 표시된다.</t>
+          <t xml:space="preserve">기간을 요구하지 않고 현재 자료를 보여준다.</t>
         </is>
       </c>
       <c r="G69" s="3"/>
@@ -1973,42 +1977,308 @@
       <c r="B70" s="4"/>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 응답 형식 오류 상황에서 안내 문구를 확인한다.</t>
+          <t xml:space="preserve">본문 상단 다섯 절을 확인한다.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">형식이 잘못된 AI 응답</t>
+          <t xml:space="preserve">프로젝트·태스크·일정 자료</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 실패 안내가 표시되고 원문 응답은 노출되지 않는다.</t>
+          <t xml:space="preserve">프로젝트 기본 정보·진행 상태 요약·주요 성과·일정 이슈·향후 계획이 DB 값으로 생성된다.</t>
         </is>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="2"/>
     </row>
+    <row r="71" ht="38" customHeight="1">
+      <c r="A71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세 표의 문서·태스크·결정·일정·금액을 확인한다.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">승인·대기·거절 자료 혼합</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">승인 계약과 유효 snapshot에 맞는 현재 자료만 포함된다.</t>
+        </is>
+      </c>
+      <c r="G71" s="3"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" ht="38" customHeight="1">
+      <c r="A72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MD·HTML·XLSX·PDF로 프로젝트 현황을 생성한다.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네 출력 형식</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네 형식 모두 같은 절과 자료를 가진 파일이 생성된다.</t>
+        </is>
+      </c>
+      <c r="G72" s="3"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" ht="38" customHeight="1">
+      <c r="A73" s="3"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이력에서 파일을 다시 내려받고 VIEWER로도 다운로드한다.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성된 산출물 ID</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제목 기반 파일명으로 다운로드되며 VIEWER 조회는 허용된다.</t>
+        </is>
+      </c>
+      <c r="G73" s="3"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" ht="38" customHeight="1">
+      <c r="A74" s="3"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원천 자료 추가와 201건 이상 절을 확인한다.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 후 문서 추가·항목 201건</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stale가 표시되고 200건 상한이면 생략 건수가 사용자에게 안내된다.</t>
+        </is>
+      </c>
+      <c r="G74" s="3"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" ht="38" customHeight="1">
+      <c r="A75" s="3"/>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리 실패·재시도·오류 안내</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서를 업로드하고 처리 상태를 확인한다.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정상 문서</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리 중 상태가 화면에 표시된다.</t>
+        </is>
+      </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" ht="38" customHeight="1">
+      <c r="A76" s="3"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리 실패 문서의 상태와 사유를 확인한다.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추출 실패 문서</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실패 상태와 사용자가 이해할 수 있는 사유가 표시된다.</t>
+        </is>
+      </c>
+      <c r="G76" s="3"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" ht="38" customHeight="1">
+      <c r="A77" s="3"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실패 문서의 재시도를 실행한다.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재시도 가능한 문서</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리가 다시 시작되고 최종 상태로 변경된다.</t>
+        </is>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" ht="38" customHeight="1">
+      <c r="A78" s="3"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리 중 서비스 재시작 후 화면을 새로고침한다.</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리 중 문서</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업이 유실되지 않고 완료 또는 실패 상태로 표시된다.</t>
+        </is>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" ht="38" customHeight="1">
+      <c r="A79" s="3"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 연결 실패 상황에서 안내 문구를 확인한다.</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 서버 연결 실패</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 연결 오류 안내와 재시도 방법이 표시된다.</t>
+        </is>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" ht="38" customHeight="1">
+      <c r="A80" s="3"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 응답 형식 오류 상황에서 안내 문구를 확인한다.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">형식이 잘못된 AI 응답</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석 실패 안내가 표시되고 원문 응답은 노출되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="B36:B43"/>
+    <mergeCell ref="B44:B49"/>
     <mergeCell ref="B50:B54"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="B59:B64"/>
-    <mergeCell ref="B65:B70"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="B65:B68"/>
+    <mergeCell ref="B69:B74"/>
+    <mergeCell ref="B75:B80"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
